--- a/docs/BufferC-PLC寄存器表_V8.xlsx
+++ b/docs/BufferC-PLC寄存器表_V8.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="读取区" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="318">
   <si>
     <t>序号</t>
   </si>
@@ -67,15 +67,33 @@
     <t>【各站货物状态区】</t>
   </si>
   <si>
+    <t xml:space="preserve">0=空 1=（AGV）有货已存储 2=AGV正在放货 3=AGV正在取货 4=报警 5= （人工）有货已存储  </t>
+  </si>
+  <si>
+    <t>1、AGV侧
+ a）入货逻辑
+ 0 ——》 2 ——》1 表示AGV完整入货流程
+ bufferc采集 该数据变化 给PLC测写入货物Id
+ b）出货逻辑
+ 1——》3——》0 or 1——》0AGV完整出货流程
+ bufferc采集完整流程给MCS上报 ，给PLC删除货物Id
+2、手动侧
+ a）入货测
+ 0——》5 5长保持
+ 采集状态为手动入货
+ b）出货侧
+ 5——》3——》0 or 5——》0</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>站1 货物状态</t>
+  </si>
+  <si>
     <t>0=空 1=有货已存储 2=AGV正在放货 3=AGV正在取货 4=报警</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>站1 货物状态</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -178,6 +196,12 @@
     <t>站1 报警码</t>
   </si>
   <si>
+    <t>0=正常 N=报警码(0~65535) 1 2 3 4 10</t>
+  </si>
+  <si>
+    <t>1 2 3 4 10 报警</t>
+  </si>
+  <si>
     <t>19</t>
   </si>
   <si>
@@ -274,9 +298,6 @@
     <t>0=正常(InService) 1=禁用(OutOfService)</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>站1 控制状态</t>
   </si>
   <si>
@@ -643,16 +664,23 @@
     <t>BufferC检测340=1后处理，完成后写0应答 [V8: 229-&gt;340]</t>
   </si>
   <si>
-    <t>扫描应答</t>
-  </si>
-  <si>
-    <t>0=已确认。地址340双用: PLC写1上报, BufferC写0应答 [V8变更]</t>
-  </si>
-  <si>
     <t>【各站操作命令】</t>
   </si>
   <si>
     <t>0=无 1=写入货物ID 2=删除货物ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1、写寄存器
+发命令前 Bufferc来清楚400（不包括400）以上的寄存器内容为空（0值）
+发送命令流程
+1、先写入操作命令 或者货物ID 修改完毕后
+2、写入400（新值） 
+PLC通过400值的变化
+1、来去扫描401——672的数值变化 来处理对应逻辑
+2、回传400的值给到306 
+Bufferc通过306 判断PLC接受命令成功与否 
+重发 N次 然后
+</t>
   </si>
   <si>
     <t>401</t>
@@ -989,7 +1017,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1013,13 +1041,6 @@
       <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1166,7 +1187,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1188,6 +1209,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
@@ -1502,152 +1529,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1666,6 +1693,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2014,8 +2053,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:K94"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2073,7 +2112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:4">
+    <row r="5" ht="15" spans="1:11">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>11</v>
@@ -2082,267 +2121,394 @@
       <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:4">
+      <c r="E5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:11">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:4">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:11">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:11">
       <c r="A10" s="4">
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:11">
       <c r="A11" s="4">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:11">
       <c r="A12" s="4">
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:11">
       <c r="A13" s="4">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="4">
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:11">
       <c r="A15" s="4">
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:11">
       <c r="A16" s="4">
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:11">
       <c r="A17" s="4">
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:11">
       <c r="A18" s="4">
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:11">
       <c r="A19" s="4">
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:11">
       <c r="A20" s="4">
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:11">
       <c r="A21" s="4">
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>12</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" ht="15" spans="1:4">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:8">
       <c r="A23" s="4">
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
     </row>
     <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="4">
         <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -2350,13 +2516,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -2364,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -2378,13 +2544,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -2392,13 +2558,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -2406,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:4">
@@ -2420,13 +2586,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:4">
@@ -2434,13 +2600,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
@@ -2448,13 +2614,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:4">
@@ -2462,13 +2628,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
@@ -2476,13 +2642,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
@@ -2490,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
@@ -2504,13 +2670,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
@@ -2518,13 +2684,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:4">
@@ -2532,37 +2698,37 @@
         <v>34</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" ht="15" spans="1:4">
       <c r="A39" s="6"/>
       <c r="B39" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:4">
       <c r="A40" s="4">
         <v>35</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>81</v>
+      <c r="B40" s="4">
+        <v>34</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:4">
@@ -2570,13 +2736,13 @@
         <v>36</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:4">
@@ -2584,13 +2750,13 @@
         <v>37</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:4">
@@ -2598,13 +2764,13 @@
         <v>38</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:4">
@@ -2612,13 +2778,13 @@
         <v>39</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:4">
@@ -2626,13 +2792,13 @@
         <v>40</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:4">
@@ -2640,13 +2806,13 @@
         <v>41</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:4">
@@ -2654,13 +2820,13 @@
         <v>42</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:4">
@@ -2668,13 +2834,13 @@
         <v>43</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:4">
@@ -2682,13 +2848,13 @@
         <v>44</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:4">
@@ -2696,13 +2862,13 @@
         <v>45</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:4">
@@ -2710,13 +2876,13 @@
         <v>46</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:4">
@@ -2724,13 +2890,13 @@
         <v>47</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:4">
@@ -2738,13 +2904,13 @@
         <v>48</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:4">
@@ -2752,13 +2918,13 @@
         <v>49</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:4">
@@ -2766,23 +2932,23 @@
         <v>50</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" ht="15" spans="1:4">
       <c r="A56" s="6"/>
       <c r="B56" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:4">
@@ -2790,13 +2956,13 @@
         <v>51</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:4">
@@ -2804,13 +2970,13 @@
         <v>52</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:4">
@@ -2818,13 +2984,13 @@
         <v>53</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:4">
@@ -2832,13 +2998,13 @@
         <v>54</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:4">
@@ -2846,13 +3012,13 @@
         <v>55</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:4">
@@ -2860,13 +3026,13 @@
         <v>56</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:4">
@@ -2874,13 +3040,13 @@
         <v>57</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:4">
@@ -2888,13 +3054,13 @@
         <v>58</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:4">
@@ -2902,13 +3068,13 @@
         <v>59</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:4">
@@ -2916,13 +3082,13 @@
         <v>60</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" ht="16.5" spans="1:4">
@@ -2930,13 +3096,13 @@
         <v>61</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:4">
@@ -2944,13 +3110,13 @@
         <v>62</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:4">
@@ -2958,13 +3124,13 @@
         <v>63</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:4">
@@ -2972,13 +3138,13 @@
         <v>64</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:4">
@@ -2986,13 +3152,13 @@
         <v>65</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:4">
@@ -3000,23 +3166,23 @@
         <v>66</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" ht="15" spans="1:4">
       <c r="A73" s="6"/>
       <c r="B73" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:4">
@@ -3024,13 +3190,13 @@
         <v>67</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="75" ht="16.5" spans="1:4">
@@ -3038,37 +3204,37 @@
         <v>68</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:4">
-      <c r="A76" s="7">
+      <c r="A76" s="11">
         <v>69</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>159</v>
+      <c r="B76" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="77" ht="15" spans="1:4">
       <c r="A77" s="6"/>
       <c r="B77" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C77" s="6"/>
       <c r="D77" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:4">
@@ -3076,10 +3242,10 @@
         <v>70</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D78" s="7"/>
     </row>
@@ -3088,13 +3254,13 @@
         <v>71</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:4">
@@ -3102,13 +3268,13 @@
         <v>72</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:4">
@@ -3116,13 +3282,13 @@
         <v>73</v>
       </c>
       <c r="B81" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D81" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:4">
@@ -3130,13 +3296,13 @@
         <v>74</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:4">
@@ -3144,13 +3310,13 @@
         <v>75</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:4">
@@ -3158,13 +3324,13 @@
         <v>76</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:4">
@@ -3172,13 +3338,13 @@
         <v>77</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:4">
@@ -3186,13 +3352,13 @@
         <v>78</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:4">
@@ -3200,13 +3366,13 @@
         <v>79</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:4">
@@ -3214,13 +3380,13 @@
         <v>80</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:4">
@@ -3228,13 +3394,13 @@
         <v>81</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:4">
@@ -3242,13 +3408,13 @@
         <v>82</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:4">
@@ -3256,13 +3422,13 @@
         <v>83</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:4">
@@ -3270,13 +3436,13 @@
         <v>84</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:4">
@@ -3284,13 +3450,13 @@
         <v>85</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:4">
@@ -3298,16 +3464,20 @@
         <v>86</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E5:K21"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3316,8 +3486,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3342,11 +3512,11 @@
     <row r="2" ht="15" spans="1:4">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
@@ -3354,295 +3524,433 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:4">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
-      <c r="A5" s="7">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="1:4">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" ht="15" spans="1:12">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:4">
+        <v>208</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:12">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:12">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:4">
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:12">
       <c r="A9" s="4">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:12">
       <c r="A10" s="4">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:12">
       <c r="A11" s="4">
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:12">
       <c r="A12" s="4">
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:12">
       <c r="A13" s="4">
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:12">
       <c r="A14" s="4">
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:12">
       <c r="A15" s="4">
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:12">
       <c r="A16" s="4">
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:12">
       <c r="A17" s="4">
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:12">
       <c r="A18" s="4">
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:12">
       <c r="A19" s="4">
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:12">
       <c r="A20" s="4">
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:12">
       <c r="A21" s="4">
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:12">
       <c r="A22" s="4">
         <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:4">
+        <v>212</v>
+      </c>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" ht="15" spans="1:12">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
-        <v>242</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
     </row>
     <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="7">
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -3650,13 +3958,13 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>247</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -3664,13 +3972,13 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -3678,13 +3986,13 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -3692,13 +4000,13 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -3706,13 +4014,13 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:4">
@@ -3720,13 +4028,13 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:4">
@@ -3734,13 +4042,13 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
@@ -3748,13 +4056,13 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:4">
@@ -3762,13 +4070,13 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
@@ -3776,13 +4084,13 @@
         <v>29</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
@@ -3790,13 +4098,13 @@
         <v>30</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
@@ -3804,13 +4112,13 @@
         <v>31</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
@@ -3818,13 +4126,13 @@
         <v>32</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:4">
@@ -3832,13 +4140,13 @@
         <v>33</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:4">
@@ -3846,16 +4154,19 @@
         <v>34</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:L23"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3874,167 +4185,167 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="3" ht="15" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" ht="16.5" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" ht="16.5" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C12" s="2"/>
     </row>
     <row r="13" ht="16.5" spans="1:3">
       <c r="A13" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" ht="16.5" spans="1:3">
       <c r="A14" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C14" s="2"/>
     </row>
     <row r="15" ht="16.5" spans="1:3">
       <c r="A15" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="16" ht="16.5" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" ht="16.5" spans="1:3">
       <c r="A17" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" ht="16.5" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C18" s="2"/>
     </row>
     <row r="20" ht="18" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>3</v>
@@ -4042,24 +4353,24 @@
     </row>
     <row r="22" ht="16.5" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/docs/BufferC-PLC寄存器表_V8.xlsx
+++ b/docs/BufferC-PLC寄存器表_V8.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="321">
   <si>
     <t>序号</t>
   </si>
@@ -75,7 +75,7 @@
  0 ——》 2 ——》1 表示AGV完整入货流程
  bufferc采集 该数据变化 给PLC测写入货物Id
  b）出货逻辑
- 1——》3——》0 or 1——》0AGV完整出货流程
+ 1——》3——》0 or 1——》0 AGV完整出货流程
  bufferc采集完整流程给MCS上报 ，给PLC删除货物Id
 2、手动侧
  a）入货测
@@ -91,27 +91,36 @@
     <t>站1 货物状态</t>
   </si>
   <si>
+    <t xml:space="preserve">0=空 1=有货已存储 2=AGV正在放货 3=AGV正在取货   5= （人工）有货已存储  </t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>站2 货物状态</t>
+  </si>
+  <si>
+    <t>0=空 1=有货已存储 2=AGV正在放货 3=AGV正在取货</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>站3 货物状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0=空 1=有货已存储 2=AGV正在放货 3=AGV正在取货 </t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>站4 货物状态</t>
+  </si>
+  <si>
     <t>0=空 1=有货已存储 2=AGV正在放货 3=AGV正在取货 4=报警</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>站2 货物状态</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>站3 货物状态</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>站4 货物状态</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -415,6 +424,12 @@
     <t>站2 货物ID</t>
   </si>
   <si>
+    <t>plc待处理问题：
+1、去掉货物状态 中的4=报警 
+2、控制状态 对应 0是上线模式 1是下线模式
+3、条码扫描 流程确定是否ok</t>
+  </si>
+  <si>
     <t>82~97</t>
   </si>
   <si>
@@ -521,9 +536,6 @@
   </si>
   <si>
     <t>16寄存器=32字符ASCII [V8: 8reg-&gt;16reg]</t>
-  </si>
-  <si>
-    <t>340</t>
   </si>
   <si>
     <t>握手标志 (读/写双用)</t>
@@ -1674,7 +1686,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1703,6 +1715,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2163,7 +2181,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -2178,13 +2196,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -2199,13 +2217,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -2220,13 +2238,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
@@ -2241,13 +2259,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
@@ -2262,13 +2280,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
@@ -2283,13 +2301,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -2304,13 +2322,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -2325,13 +2343,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -2346,13 +2364,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -2367,13 +2385,13 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -2388,13 +2406,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -2409,13 +2427,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -2430,13 +2448,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -2451,13 +2469,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -2470,11 +2488,11 @@
     <row r="22" ht="15" spans="1:4">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:8">
@@ -2482,16 +2500,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -2502,13 +2520,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -2516,13 +2534,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -2530,13 +2548,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -2544,13 +2562,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -2558,13 +2576,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -2572,13 +2590,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:4">
@@ -2586,13 +2604,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:4">
@@ -2600,13 +2618,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
@@ -2614,13 +2632,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:4">
@@ -2628,13 +2646,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
@@ -2642,13 +2660,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
@@ -2656,13 +2674,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
@@ -2670,13 +2688,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
@@ -2684,13 +2702,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:4">
@@ -2698,23 +2716,23 @@
         <v>34</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" ht="15" spans="1:4">
       <c r="A39" s="6"/>
       <c r="B39" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:4">
@@ -2725,10 +2743,10 @@
         <v>34</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:4">
@@ -2736,13 +2754,13 @@
         <v>36</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:4">
@@ -2750,13 +2768,13 @@
         <v>37</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:4">
@@ -2764,13 +2782,13 @@
         <v>38</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:4">
@@ -2778,13 +2796,13 @@
         <v>39</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:4">
@@ -2792,13 +2810,13 @@
         <v>40</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:4">
@@ -2806,13 +2824,13 @@
         <v>41</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:4">
@@ -2820,13 +2838,13 @@
         <v>42</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:4">
@@ -2834,13 +2852,13 @@
         <v>43</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:4">
@@ -2848,13 +2866,13 @@
         <v>44</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:4">
@@ -2862,13 +2880,13 @@
         <v>45</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:4">
@@ -2876,13 +2894,13 @@
         <v>46</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:4">
@@ -2890,13 +2908,13 @@
         <v>47</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:4">
@@ -2904,13 +2922,13 @@
         <v>48</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:4">
@@ -2918,13 +2936,13 @@
         <v>49</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:4">
@@ -2932,23 +2950,23 @@
         <v>50</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" ht="15" spans="1:4">
       <c r="A56" s="6"/>
       <c r="B56" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:4">
@@ -2956,285 +2974,382 @@
         <v>51</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:10">
       <c r="A58" s="7">
         <v>52</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="59" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="12"/>
+    </row>
+    <row r="59" ht="16.5" spans="1:10">
       <c r="A59" s="7">
         <v>53</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:4">
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="12"/>
+    </row>
+    <row r="60" ht="16.5" spans="1:10">
       <c r="A60" s="7">
         <v>54</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="12"/>
+    </row>
+    <row r="61" ht="16.5" spans="1:10">
       <c r="A61" s="7">
         <v>55</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="12"/>
+    </row>
+    <row r="62" ht="16.5" spans="1:10">
       <c r="A62" s="7">
         <v>56</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="12"/>
+    </row>
+    <row r="63" ht="16.5" spans="1:10">
       <c r="A63" s="7">
         <v>57</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="12"/>
+    </row>
+    <row r="64" ht="16.5" spans="1:10">
       <c r="A64" s="7">
         <v>58</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="12"/>
+    </row>
+    <row r="65" ht="16.5" spans="1:10">
       <c r="A65" s="7">
         <v>59</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="12"/>
+    </row>
+    <row r="66" ht="16.5" spans="1:10">
       <c r="A66" s="7">
         <v>60</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+    </row>
+    <row r="67" ht="16.5" spans="1:10">
       <c r="A67" s="7">
         <v>61</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+    </row>
+    <row r="68" ht="16.5" spans="1:10">
       <c r="A68" s="7">
         <v>62</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="69" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+    </row>
+    <row r="69" ht="16.5" spans="1:10">
       <c r="A69" s="7">
         <v>63</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="70" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+    </row>
+    <row r="70" ht="16.5" spans="1:10">
       <c r="A70" s="7">
         <v>64</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+    </row>
+    <row r="71" ht="16.5" spans="1:10">
       <c r="A71" s="7">
         <v>65</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72" ht="16.5" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+    </row>
+    <row r="72" ht="16.5" spans="1:10">
       <c r="A72" s="7">
         <v>66</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="73" ht="15" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+    </row>
+    <row r="73" ht="15" spans="1:10">
       <c r="A73" s="6"/>
       <c r="B73" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="74" ht="16.5" spans="1:4">
+        <v>157</v>
+      </c>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+    </row>
+    <row r="74" ht="16.5" spans="1:10">
       <c r="A74" s="7">
         <v>67</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:4">
+        <v>160</v>
+      </c>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+    </row>
+    <row r="75" ht="16.5" spans="1:10">
       <c r="A75" s="7">
         <v>68</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="76" ht="16.5" spans="1:4">
-      <c r="A76" s="11">
+        <v>163</v>
+      </c>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
+    </row>
+    <row r="76" ht="16.5" spans="1:10">
+      <c r="A76" s="13">
         <v>69</v>
       </c>
-      <c r="B76" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>162</v>
-      </c>
+      <c r="B76" s="13">
+        <v>340</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
     </row>
     <row r="77" ht="15" spans="1:4">
       <c r="A77" s="6"/>
       <c r="B77" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C77" s="6"/>
       <c r="D77" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:4">
@@ -3242,10 +3357,10 @@
         <v>70</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D78" s="7"/>
     </row>
@@ -3254,13 +3369,13 @@
         <v>71</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" ht="16.5" spans="1:4">
@@ -3268,13 +3383,13 @@
         <v>72</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" ht="16.5" spans="1:4">
@@ -3282,13 +3397,13 @@
         <v>73</v>
       </c>
       <c r="B81" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D81" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="82" ht="16.5" spans="1:4">
@@ -3296,13 +3411,13 @@
         <v>74</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" ht="16.5" spans="1:4">
@@ -3310,13 +3425,13 @@
         <v>75</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" ht="16.5" spans="1:4">
@@ -3324,13 +3439,13 @@
         <v>76</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" ht="16.5" spans="1:4">
@@ -3338,13 +3453,13 @@
         <v>77</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" ht="16.5" spans="1:4">
@@ -3352,13 +3467,13 @@
         <v>78</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" ht="16.5" spans="1:4">
@@ -3366,13 +3481,13 @@
         <v>79</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" ht="16.5" spans="1:4">
@@ -3380,13 +3495,13 @@
         <v>80</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="89" ht="16.5" spans="1:4">
@@ -3394,13 +3509,13 @@
         <v>81</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" ht="16.5" spans="1:4">
@@ -3408,13 +3523,13 @@
         <v>82</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="91" ht="16.5" spans="1:4">
@@ -3422,13 +3537,13 @@
         <v>83</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:4">
@@ -3436,13 +3551,13 @@
         <v>84</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:4">
@@ -3450,13 +3565,13 @@
         <v>85</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:4">
@@ -3464,19 +3579,20 @@
         <v>86</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="E23:H23"/>
     <mergeCell ref="E5:K21"/>
+    <mergeCell ref="F58:I65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3512,11 +3628,11 @@
     <row r="2" ht="15" spans="1:4">
       <c r="A2" s="6"/>
       <c r="B2" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
@@ -3524,23 +3640,23 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" ht="15" spans="1:4">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
@@ -3552,14 +3668,14 @@
     <row r="6" ht="15" spans="1:12">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -3574,13 +3690,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -3596,13 +3712,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -3618,13 +3734,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -3640,13 +3756,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -3662,13 +3778,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
@@ -3684,13 +3800,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
@@ -3706,13 +3822,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
@@ -3728,13 +3844,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
@@ -3750,13 +3866,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
@@ -3772,13 +3888,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -3794,13 +3910,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -3816,13 +3932,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
@@ -3838,13 +3954,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -3860,13 +3976,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -3882,13 +3998,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
@@ -3904,13 +4020,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
@@ -3924,11 +4040,11 @@
     <row r="23" ht="15" spans="1:12">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -3944,13 +4060,13 @@
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -3958,13 +4074,13 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -3972,13 +4088,13 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -3986,13 +4102,13 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -4000,13 +4116,13 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -4014,13 +4130,13 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:4">
@@ -4028,13 +4144,13 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:4">
@@ -4042,13 +4158,13 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
@@ -4056,13 +4172,13 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:4">
@@ -4070,13 +4186,13 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
@@ -4084,13 +4200,13 @@
         <v>29</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
@@ -4098,13 +4214,13 @@
         <v>30</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
@@ -4112,13 +4228,13 @@
         <v>31</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
@@ -4126,13 +4242,13 @@
         <v>32</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:4">
@@ -4140,13 +4256,13 @@
         <v>33</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:4">
@@ -4154,13 +4270,13 @@
         <v>34</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -4185,167 +4301,167 @@
   <sheetData>
     <row r="1" ht="18" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="3" ht="15" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
     <row r="11" ht="16.5" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" ht="16.5" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C12" s="2"/>
     </row>
     <row r="13" ht="16.5" spans="1:3">
       <c r="A13" s="5" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" ht="16.5" spans="1:3">
       <c r="A14" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C14" s="2"/>
     </row>
     <row r="15" ht="16.5" spans="1:3">
       <c r="A15" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="16" ht="16.5" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" ht="16.5" spans="1:3">
       <c r="A17" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" ht="16.5" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C18" s="2"/>
     </row>
     <row r="20" ht="18" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" ht="15" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>3</v>
@@ -4353,24 +4469,24 @@
     </row>
     <row r="22" ht="16.5" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/docs/BufferC-PLC寄存器表_V8.xlsx
+++ b/docs/BufferC-PLC寄存器表_V8.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="读取区" sheetId="1" r:id="rId1"/>
@@ -1583,7 +1583,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1603,7 +1603,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2412,10 +2411,10 @@
       <c r="D24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" ht="16.5" spans="1:8">
       <c r="A25" s="3">
@@ -2430,10 +2429,10 @@
       <c r="D25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" ht="16.5" spans="1:8">
       <c r="A26" s="3">
@@ -2448,10 +2447,10 @@
       <c r="D26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
     </row>
     <row r="27" ht="16.5" spans="1:8">
       <c r="A27" s="3">
@@ -2466,10 +2465,10 @@
       <c r="D27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
     </row>
     <row r="28" ht="16.5" spans="1:8">
       <c r="A28" s="3">
@@ -2484,10 +2483,10 @@
       <c r="D28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
     </row>
     <row r="29" ht="16.5" spans="1:8">
       <c r="A29" s="3">
@@ -2502,10 +2501,10 @@
       <c r="D29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
     </row>
     <row r="30" ht="16.5" spans="1:4">
       <c r="A30" s="3">
@@ -2910,7 +2909,7 @@
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="9"/>
+      <c r="J58" s="8"/>
     </row>
     <row r="59" ht="16.5" spans="1:10">
       <c r="A59" s="6">
@@ -2929,7 +2928,7 @@
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="9"/>
+      <c r="J59" s="8"/>
     </row>
     <row r="60" ht="16.5" spans="1:10">
       <c r="A60" s="6">
@@ -2948,7 +2947,7 @@
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="9"/>
+      <c r="J60" s="8"/>
     </row>
     <row r="61" ht="16.5" spans="1:10">
       <c r="A61" s="6">
@@ -2967,7 +2966,7 @@
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="9"/>
+      <c r="J61" s="8"/>
     </row>
     <row r="62" ht="16.5" spans="1:10">
       <c r="A62" s="6">
@@ -2986,7 +2985,7 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="9"/>
+      <c r="J62" s="8"/>
     </row>
     <row r="63" ht="16.5" spans="1:10">
       <c r="A63" s="6">
@@ -3005,7 +3004,7 @@
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="9"/>
+      <c r="J63" s="8"/>
     </row>
     <row r="64" ht="16.5" spans="1:10">
       <c r="A64" s="6">
@@ -3024,7 +3023,7 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="9"/>
+      <c r="J64" s="8"/>
     </row>
     <row r="65" ht="16.5" spans="1:10">
       <c r="A65" s="6">
@@ -3043,7 +3042,7 @@
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="9"/>
+      <c r="J65" s="8"/>
     </row>
     <row r="66" ht="16.5" spans="1:10">
       <c r="A66" s="6">
@@ -3058,11 +3057,11 @@
       <c r="D66" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="9"/>
-      <c r="J66" s="9"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
     </row>
     <row r="67" ht="16.5" spans="1:10">
       <c r="A67" s="6">
@@ -3077,11 +3076,11 @@
       <c r="D67" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="9"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
     </row>
     <row r="68" ht="16.5" spans="1:10">
       <c r="A68" s="6">
@@ -3096,11 +3095,11 @@
       <c r="D68" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
     </row>
     <row r="69" ht="16.5" spans="1:10">
       <c r="A69" s="6">
@@ -3115,11 +3114,11 @@
       <c r="D69" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="9"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
     </row>
     <row r="70" ht="16.5" spans="1:10">
       <c r="A70" s="6">
@@ -3134,11 +3133,11 @@
       <c r="D70" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="9"/>
-      <c r="J70" s="9"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
     </row>
     <row r="71" ht="16.5" spans="1:10">
       <c r="A71" s="6">
@@ -3153,11 +3152,11 @@
       <c r="D71" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
     </row>
     <row r="72" ht="16.5" spans="1:10">
       <c r="A72" s="6">
@@ -3172,11 +3171,11 @@
       <c r="D72" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
     </row>
     <row r="73" ht="15" spans="1:10">
       <c r="A73" s="2"/>
@@ -3187,11 +3186,11 @@
       <c r="D73" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
     </row>
     <row r="74" ht="16.5" spans="1:10">
       <c r="A74" s="6">
@@ -3206,11 +3205,11 @@
       <c r="D74" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
     </row>
     <row r="75" ht="16.5" spans="1:10">
       <c r="A75" s="6">
@@ -3225,32 +3224,29 @@
       <c r="D75" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
     </row>
     <row r="76" ht="16.5" spans="1:10">
-      <c r="A76" s="10">
+      <c r="A76" s="9">
         <v>69</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <v>340</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C76" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9"/>
-    </row>
-    <row r="77" ht="15" spans="1:4">
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+    </row>
+    <row r="77" ht="15" spans="1:8">
       <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
         <v>160</v>
@@ -3259,6 +3255,9 @@
       <c r="D77" s="2" t="s">
         <v>161</v>
       </c>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
     </row>
     <row r="78" ht="16.5" spans="1:4">
       <c r="A78" s="6">

--- a/docs/BufferC-PLC寄存器表_V8.xlsx
+++ b/docs/BufferC-PLC寄存器表_V8.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fuzif\Desktop\BufferC\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="13455"/>
   </bookViews>
   <sheets>
     <sheet name="读取区" sheetId="1" r:id="rId1"/>
@@ -1965,7 +1970,7 @@
     <col min="4" max="4" width="92.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:4">
+    <row r="1" ht="15" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1979,7 +1984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:4">
+    <row r="2" ht="15" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -1987,7 +1992,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" ht="16.5" spans="1:4">
+    <row r="3" ht="16.5" spans="1:11">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2001,7 +2006,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:4">
+    <row r="4" ht="16.5" spans="1:11">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2370,7 +2375,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" ht="15" spans="1:4">
+    <row r="22" ht="15" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
         <v>47</v>
@@ -2380,7 +2385,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:8">
+    <row r="23" ht="16.5" spans="1:11">
       <c r="A23" s="3">
         <v>19</v>
       </c>
@@ -2398,7 +2403,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" ht="16.5" spans="1:8">
+    <row r="24" ht="16.5" spans="1:11">
       <c r="A24" s="3">
         <v>20</v>
       </c>
@@ -2416,7 +2421,7 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" ht="16.5" spans="1:8">
+    <row r="25" ht="16.5" spans="1:11">
       <c r="A25" s="3">
         <v>21</v>
       </c>
@@ -2434,7 +2439,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" ht="16.5" spans="1:8">
+    <row r="26" ht="16.5" spans="1:11">
       <c r="A26" s="3">
         <v>22</v>
       </c>
@@ -2452,7 +2457,7 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" ht="16.5" spans="1:8">
+    <row r="27" ht="16.5" spans="1:11">
       <c r="A27" s="3">
         <v>23</v>
       </c>
@@ -2470,7 +2475,7 @@
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" ht="16.5" spans="1:8">
+    <row r="28" ht="16.5" spans="1:11">
       <c r="A28" s="3">
         <v>24</v>
       </c>
@@ -2488,7 +2493,7 @@
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" ht="16.5" spans="1:8">
+    <row r="29" ht="16.5" spans="1:11">
       <c r="A29" s="3">
         <v>25</v>
       </c>
@@ -2506,7 +2511,7 @@
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" ht="16.5" spans="1:4">
+    <row r="30" ht="16.5" spans="1:11">
       <c r="A30" s="3">
         <v>26</v>
       </c>
@@ -2520,7 +2525,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" ht="16.5" spans="1:4">
+    <row r="31" ht="16.5" spans="1:11">
       <c r="A31" s="3">
         <v>27</v>
       </c>
@@ -2534,7 +2539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="1:4">
+    <row r="32" ht="16.5" spans="1:11">
       <c r="A32" s="3">
         <v>28</v>
       </c>
@@ -2768,7 +2773,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:4">
+    <row r="49" ht="16.5" spans="1:10">
       <c r="A49" s="3">
         <v>44</v>
       </c>
@@ -2782,7 +2787,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" ht="16.5" spans="1:4">
+    <row r="50" ht="16.5" spans="1:10">
       <c r="A50" s="3">
         <v>45</v>
       </c>
@@ -2796,7 +2801,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" ht="16.5" spans="1:4">
+    <row r="51" ht="16.5" spans="1:10">
       <c r="A51" s="3">
         <v>46</v>
       </c>
@@ -2810,7 +2815,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" ht="16.5" spans="1:4">
+    <row r="52" ht="16.5" spans="1:10">
       <c r="A52" s="3">
         <v>47</v>
       </c>
@@ -2824,7 +2829,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" ht="16.5" spans="1:4">
+    <row r="53" ht="16.5" spans="1:10">
       <c r="A53" s="3">
         <v>48</v>
       </c>
@@ -2838,7 +2843,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" ht="16.5" spans="1:4">
+    <row r="54" ht="16.5" spans="1:10">
       <c r="A54" s="3">
         <v>49</v>
       </c>
@@ -2852,7 +2857,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" ht="16.5" spans="1:4">
+    <row r="55" ht="16.5" spans="1:10">
       <c r="A55" s="3">
         <v>50</v>
       </c>
@@ -2866,7 +2871,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" ht="15" spans="1:4">
+    <row r="56" ht="15" spans="1:10">
       <c r="A56" s="2"/>
       <c r="B56" s="2" t="s">
         <v>115</v>
@@ -2876,7 +2881,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="57" ht="16.5" spans="1:4">
+    <row r="57" ht="16.5" spans="1:10">
       <c r="A57" s="6">
         <v>51</v>
       </c>
@@ -3246,7 +3251,7 @@
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
     </row>
-    <row r="77" ht="15" spans="1:8">
+    <row r="77" ht="15" spans="1:10">
       <c r="A77" s="2"/>
       <c r="B77" s="2" t="s">
         <v>160</v>
@@ -3259,7 +3264,7 @@
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
     </row>
-    <row r="78" ht="16.5" spans="1:4">
+    <row r="78" ht="16.5" spans="1:10">
       <c r="A78" s="6">
         <v>70</v>
       </c>
@@ -3273,7 +3278,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="79" ht="16.5" spans="1:4">
+    <row r="79" ht="16.5" spans="1:10">
       <c r="A79" s="6">
         <v>71</v>
       </c>
@@ -3287,7 +3292,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="80" ht="16.5" spans="1:4">
+    <row r="80" ht="16.5" spans="1:10">
       <c r="A80" s="6">
         <v>72</v>
       </c>
@@ -3519,7 +3524,7 @@
     <col min="4" max="4" width="101.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:4">
+    <row r="1" ht="15" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3533,7 +3538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:4">
+    <row r="2" ht="15" spans="1:12">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>213</v>
@@ -3543,7 +3548,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:4">
+    <row r="3" ht="16.5" spans="1:12">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3947,7 +3952,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" ht="16.5" spans="1:4">
+    <row r="22" ht="16.5" spans="1:12">
       <c r="A22" s="6">
         <v>19</v>
       </c>
@@ -3961,7 +3966,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:4">
+    <row r="23" ht="16.5" spans="1:12">
       <c r="A23" s="6">
         <v>20</v>
       </c>
@@ -3975,7 +3980,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="24" ht="16.5" spans="1:4">
+    <row r="24" ht="16.5" spans="1:12">
       <c r="A24" s="6">
         <v>21</v>
       </c>
@@ -3989,7 +3994,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:4">
+    <row r="25" ht="16.5" spans="1:12">
       <c r="A25" s="6">
         <v>22</v>
       </c>
@@ -4003,7 +4008,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:4">
+    <row r="26" ht="16.5" spans="1:12">
       <c r="A26" s="6">
         <v>23</v>
       </c>
@@ -4017,7 +4022,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:4">
+    <row r="27" ht="16.5" spans="1:12">
       <c r="A27" s="6">
         <v>24</v>
       </c>
@@ -4031,7 +4036,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:4">
+    <row r="28" ht="16.5" spans="1:12">
       <c r="A28" s="6">
         <v>25</v>
       </c>
@@ -4045,7 +4050,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="29" ht="16.5" spans="1:4">
+    <row r="29" ht="16.5" spans="1:12">
       <c r="A29" s="6">
         <v>26</v>
       </c>
@@ -4059,7 +4064,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="30" ht="16.5" spans="1:4">
+    <row r="30" ht="16.5" spans="1:12">
       <c r="A30" s="6">
         <v>27</v>
       </c>
@@ -4073,7 +4078,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="31" ht="16.5" spans="1:4">
+    <row r="31" ht="16.5" spans="1:12">
       <c r="A31" s="6">
         <v>28</v>
       </c>
@@ -4087,7 +4092,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="32" ht="16.5" spans="1:4">
+    <row r="32" ht="16.5" spans="1:12">
       <c r="A32" s="6">
         <v>29</v>
       </c>
